--- a/rules/CORE-000171/negative/01/data/unit-test-coreid-CG0058-negative 1.xlsx
+++ b/rules/CORE-000171/negative/01/data/unit-test-coreid-CG0058-negative 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Source\core-contributor\rules\CORE-000171\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC1AB28-043C-47D8-B6B0-1E854E6EE3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC7703B-B994-46A4-BD3C-1E9BD524C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
